--- a/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_00.xlsx
+++ b/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_00.xlsx
@@ -564,22 +564,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -618,14 +618,14 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -638,10 +638,10 @@
         <v>12</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -663,22 +663,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -762,22 +762,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -787,43 +787,43 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.42</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0.31</v>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -833,13 +833,13 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -861,27 +861,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -891,54 +891,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U5" t="n">
         <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -960,22 +960,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,22 +985,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1010,18 +1010,18 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1031,13 +1031,13 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
         <v>4</v>
       </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
       <c r="W6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1104,16 +1104,16 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>0.47</v>
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" t="n">
         <v>5</v>
       </c>
-      <c r="V7" t="n">
-        <v>7</v>
-      </c>
       <c r="W7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1158,37 +1158,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1198,41 +1198,41 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
         <v>3</v>
@@ -1257,44 +1257,44 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>right</t>
@@ -1302,16 +1302,16 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0.2</v>
@@ -1325,16 +1325,16 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1356,47 +1356,47 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>fish</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1406,34 +1406,34 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S10" t="n">
         <v>10</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>12</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1455,84 +1455,84 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0.47</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.27</v>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>12</v>
+      </c>
+      <c r="W11" t="n">
         <v>9</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1554,39 +1554,39 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -1594,41 +1594,41 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>12</v>
       </c>
       <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V12" t="n">
         <v>9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>10</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
@@ -1653,44 +1653,44 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>center</t>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q13" t="n">
         <v>0.33</v>
@@ -1721,16 +1721,16 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
         <v>13</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1752,22 +1752,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1777,22 +1777,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1823,13 +1823,13 @@
         <v>13</v>
       </c>
       <c r="U14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1851,22 +1851,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1896,16 +1896,16 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q15" t="n">
         <v>0.2</v>
@@ -1925,10 +1925,10 @@
         <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1950,22 +1950,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2007,11 +2007,11 @@
         <v>0.47</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2021,13 +2021,13 @@
         <v>14</v>
       </c>
       <c r="U16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16" t="n">
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2079,54 +2079,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S17" t="n">
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U17" t="n">
         <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2219,13 +2219,13 @@
         <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -2247,42 +2247,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2315,16 +2315,16 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V19" t="n">
         <v>12</v>
       </c>
       <c r="W19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2396,34 +2396,34 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q20" t="n">
         <v>0.47</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S20" t="n">
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V20" t="n">
         <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -2445,44 +2445,44 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>left</t>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
+        <v>9</v>
+      </c>
+      <c r="U21" t="n">
+        <v>7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>9</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -2544,47 +2544,47 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2594,34 +2594,34 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8</v>
+      </c>
+      <c r="W22" t="n">
         <v>5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3</v>
-      </c>
-      <c r="W22" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -2643,27 +2643,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2673,54 +2673,54 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S23" t="n">
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2742,22 +2742,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2799,7 +2799,7 @@
         <v>0.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2813,13 +2813,13 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
         <v>14</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2898,7 +2898,7 @@
         <v>0.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2909,16 +2909,16 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>12</v>
       </c>
       <c r="W25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2940,27 +2940,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2990,34 +2990,34 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S26" t="n">
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>11</v>
       </c>
       <c r="V26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3039,22 +3039,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3089,18 +3089,18 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P27" t="n">
         <v>0.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3110,13 +3110,13 @@
         <v>11</v>
       </c>
       <c r="U27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="V27" t="n">
         <v>14</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -3138,22 +3138,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="Q28" t="n">
         <v>0.2</v>
@@ -3212,10 +3212,10 @@
         <v>12</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -3237,22 +3237,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3282,19 +3282,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q29" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.42</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -3311,10 +3311,10 @@
         <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W29" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3361,17 +3361,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3381,19 +3381,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.75</v>
+        <v>0.42</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -3435,27 +3435,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3465,54 +3465,54 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S31" t="n">
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U31" t="n">
         <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -3534,22 +3534,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3559,27 +3559,27 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3588,14 +3588,14 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -3605,13 +3605,13 @@
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -3633,32 +3633,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -3694,17 +3694,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S33" t="n">
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
         <v>11</v>
@@ -3732,32 +3732,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3777,19 +3777,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3800,16 +3800,16 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V34" t="n">
         <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3885,30 +3885,30 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S35" t="n">
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
         <v>9</v>
       </c>
       <c r="W35" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3930,84 +3930,84 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S36" t="n">
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -4029,52 +4029,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4083,30 +4083,30 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S37" t="n">
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -4128,84 +4128,84 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S38" t="n">
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4227,27 +4227,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4272,19 +4272,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -4295,16 +4295,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U39" t="n">
         <v>13</v>
       </c>
       <c r="V39" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="W39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -4326,22 +4326,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4351,43 +4351,43 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4397,13 +4397,13 @@
         <v>13</v>
       </c>
       <c r="U40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V40" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
@@ -4425,22 +4425,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4455,38 +4455,38 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,10 +4499,10 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W41" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
@@ -4524,22 +4524,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4549,43 +4549,43 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4595,13 +4595,13 @@
         <v>14</v>
       </c>
       <c r="U42" t="n">
+        <v>8</v>
+      </c>
+      <c r="V42" t="n">
         <v>10</v>
       </c>
-      <c r="V42" t="n">
-        <v>2</v>
-      </c>
       <c r="W42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -4623,27 +4623,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4653,54 +4653,54 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U43" t="n">
         <v>3</v>
       </c>
       <c r="V43" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W43" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
@@ -4722,22 +4722,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4757,22 +4757,22 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S44" t="n">
@@ -4793,13 +4793,13 @@
         <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -4821,42 +4821,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="P45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q45" t="n">
         <v>0.58</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.47</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4889,16 +4889,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -4920,44 +4920,44 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>right</t>
@@ -4965,19 +4965,19 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q46" t="n">
         <v>0.58</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0.4</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -4988,16 +4988,16 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
+        <v>10</v>
+      </c>
+      <c r="U46" t="n">
+        <v>9</v>
+      </c>
+      <c r="V46" t="n">
         <v>6</v>
       </c>
-      <c r="U46" t="n">
+      <c r="W46" t="n">
         <v>2</v>
-      </c>
-      <c r="V46" t="n">
-        <v>4</v>
-      </c>
-      <c r="W46" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="47">
@@ -5019,47 +5019,47 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5069,34 +5069,34 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S47" t="n">
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W47" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -5118,32 +5118,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -5186,10 +5186,10 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V48" t="n">
         <v>12</v>
@@ -5217,44 +5217,44 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>right</t>
@@ -5262,19 +5262,19 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U49" t="n">
         <v>1</v>
       </c>
       <c r="V49" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -5316,22 +5316,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5341,19 +5341,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>left</t>
@@ -5361,16 +5361,16 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Q50" t="n">
         <v>0.2</v>
@@ -5387,13 +5387,13 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
+        <v>4</v>
+      </c>
+      <c r="V50" t="n">
+        <v>12</v>
+      </c>
+      <c r="W50" t="n">
         <v>7</v>
-      </c>
-      <c r="V50" t="n">
-        <v>6</v>
-      </c>
-      <c r="W50" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -5415,84 +5415,84 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S51" t="n">
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -5514,27 +5514,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5559,19 +5559,19 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P52" t="n">
         <v>0.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.27</v>
+        <v>0.67</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -5582,16 +5582,16 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
         <v>11</v>
       </c>
       <c r="V52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -5613,22 +5613,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5658,19 +5658,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -5684,13 +5684,13 @@
         <v>11</v>
       </c>
       <c r="U53" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="V53" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -5712,22 +5712,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5747,33 +5747,33 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P54" t="n">
         <v>0.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5789,7 +5789,7 @@
         <v>1</v>
       </c>
       <c r="W54" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -5811,22 +5811,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5856,19 +5856,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Q55" t="n">
         <v>0.36</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0.25</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -5885,10 +5885,10 @@
         <v>1</v>
       </c>
       <c r="V55" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W55" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -5910,22 +5910,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5935,43 +5935,43 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5981,13 +5981,13 @@
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -6009,27 +6009,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6039,12 +6039,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -6077,16 +6077,16 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U57" t="n">
         <v>3</v>
       </c>
       <c r="V57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -6108,22 +6108,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6133,22 +6133,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6158,18 +6158,18 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -6179,13 +6179,13 @@
         <v>3</v>
       </c>
       <c r="U58" t="n">
+        <v>2</v>
+      </c>
+      <c r="V58" t="n">
         <v>4</v>
       </c>
-      <c r="V58" t="n">
-        <v>5</v>
-      </c>
       <c r="W58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -6207,52 +6207,52 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6261,30 +6261,30 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S59" t="n">
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -6306,32 +6306,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6346,17 +6346,17 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S60" t="n">
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V60" t="n">
         <v>12</v>
@@ -6405,47 +6405,47 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6455,34 +6455,34 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S61" t="n">
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U61" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V61" t="n">
+        <v>15</v>
+      </c>
+      <c r="W61" t="n">
         <v>9</v>
-      </c>
-      <c r="W61" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="62">
@@ -6504,44 +6504,44 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>left</t>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q62" t="n">
         <v>0.27</v>
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>2</v>
-      </c>
-      <c r="W62" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -6603,37 +6603,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6643,41 +6643,41 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S63" t="n">
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V63" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="W63" t="n">
         <v>6</v>
@@ -6702,84 +6702,84 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S64" t="n">
         <v>12</v>
       </c>
       <c r="T64" t="n">
+        <v>7</v>
+      </c>
+      <c r="U64" t="n">
+        <v>8</v>
+      </c>
+      <c r="V64" t="n">
         <v>9</v>
       </c>
-      <c r="U64" t="n">
+      <c r="W64" t="n">
         <v>10</v>
-      </c>
-      <c r="V64" t="n">
-        <v>11</v>
-      </c>
-      <c r="W64" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -6801,27 +6801,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q65" t="n">
         <v>0.27</v>
@@ -6869,16 +6869,16 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U65" t="n">
         <v>13</v>
       </c>
       <c r="V65" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="W65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -6900,22 +6900,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -6971,13 +6971,13 @@
         <v>13</v>
       </c>
       <c r="U66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V66" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -6999,22 +6999,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7044,16 +7044,16 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="Q67" t="n">
         <v>0.2</v>
@@ -7073,10 +7073,10 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W67" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
@@ -7098,22 +7098,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7123,17 +7123,17 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7143,19 +7143,19 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -7169,13 +7169,13 @@
         <v>14</v>
       </c>
       <c r="U68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V68" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W68" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -7197,27 +7197,27 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7227,54 +7227,54 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P69" t="n">
         <v>0.8</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S69" t="n">
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U69" t="n">
         <v>3</v>
       </c>
       <c r="V69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7321,17 +7321,17 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7341,19 +7341,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -7367,13 +7367,13 @@
         <v>3</v>
       </c>
       <c r="U70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W70" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
@@ -7395,42 +7395,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7440,19 +7440,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P71" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q71" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0.42</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -7463,16 +7463,16 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V71" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W71" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -7494,42 +7494,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7539,19 +7539,19 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -7562,16 +7562,16 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V72" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="W72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -7593,52 +7593,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7647,30 +7647,30 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S73" t="n">
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U73" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V73" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W73" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -7692,84 +7692,84 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S74" t="n">
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V74" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W74" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -7791,27 +7791,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7821,14 +7821,14 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>center</t>
@@ -7836,19 +7836,19 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P75" t="n">
         <v>0.47</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U75" t="n">
         <v>1</v>
       </c>
       <c r="V75" t="n">
+        <v>8</v>
+      </c>
+      <c r="W75" t="n">
         <v>10</v>
-      </c>
-      <c r="W75" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -7890,22 +7890,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7915,17 +7915,17 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7935,19 +7935,19 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -7961,13 +7961,13 @@
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V76" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="W76" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
@@ -7989,84 +7989,84 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S77" t="n">
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V77" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -8088,27 +8088,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8118,54 +8118,54 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q78" t="n">
         <v>0.33</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S78" t="n">
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U78" t="n">
         <v>11</v>
       </c>
       <c r="V78" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W78" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -8187,22 +8187,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8212,27 +8212,27 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -8241,14 +8241,14 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -8258,13 +8258,13 @@
         <v>11</v>
       </c>
       <c r="U79" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="V79" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W79" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
@@ -8286,22 +8286,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8336,18 +8336,18 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="Q80" t="n">
         <v>0.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -8360,10 +8360,10 @@
         <v>12</v>
       </c>
       <c r="V80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W80" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81">
@@ -8385,22 +8385,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8439,14 +8439,14 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q81" t="n">
         <v>0.31</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -8459,7 +8459,7 @@
         <v>1</v>
       </c>
       <c r="V81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W81" t="n">
         <v>13</v>
@@ -8484,22 +8484,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8509,32 +8509,32 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -8555,13 +8555,13 @@
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V82" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
@@ -8583,27 +8583,27 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8613,22 +8613,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8637,30 +8637,30 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S83" t="n">
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U83" t="n">
         <v>3</v>
       </c>
       <c r="V83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W83" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -8682,22 +8682,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_12.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -8753,7 +8753,7 @@
         <v>3</v>
       </c>
       <c r="U84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
         <v>11</v>
@@ -8781,84 +8781,84 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S85" t="n">
         <v>7</v>
       </c>
       <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>6</v>
+      </c>
+      <c r="V85" t="n">
         <v>4</v>
       </c>
-      <c r="U85" t="n">
-        <v>5</v>
-      </c>
-      <c r="V85" t="n">
-        <v>8</v>
-      </c>
       <c r="W85" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -8880,84 +8880,84 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S86" t="n">
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W86" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -8979,47 +8979,47 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9029,34 +9029,34 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q87" t="n">
         <v>0.2</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S87" t="n">
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V87" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -9078,84 +9078,84 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q88" t="n">
         <v>0.4</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S88" t="n">
         <v>10</v>
       </c>
       <c r="T88" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U88" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W88" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
@@ -9177,44 +9177,44 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_33.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>left</t>
@@ -9222,19 +9222,19 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U89" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V89" t="n">
+        <v>1</v>
+      </c>
+      <c r="W89" t="n">
         <v>10</v>
-      </c>
-      <c r="W89" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -9276,32 +9276,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/car/car_40.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9311,49 +9311,49 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P90" t="n">
         <v>0.73</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S90" t="n">
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U90" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V90" t="n">
         <v>11</v>
       </c>
       <c r="W90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -9375,27 +9375,27 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_50.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>right</t>
@@ -9429,10 +9429,10 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -9443,16 +9443,16 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U91" t="n">
         <v>13</v>
       </c>
       <c r="V91" t="n">
+        <v>12</v>
+      </c>
+      <c r="W91" t="n">
         <v>2</v>
-      </c>
-      <c r="W91" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -9474,22 +9474,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_09.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_25.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_13.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_25.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9499,43 +9499,43 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S92" t="n">
@@ -9545,13 +9545,13 @@
         <v>13</v>
       </c>
       <c r="U92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W92" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -9573,22 +9573,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9603,38 +9603,38 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="Q93" t="n">
         <v>0.2</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -9647,10 +9647,10 @@
         <v>14</v>
       </c>
       <c r="V93" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W93" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94">
@@ -9672,22 +9672,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9697,43 +9697,43 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -9743,13 +9743,13 @@
         <v>14</v>
       </c>
       <c r="U94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W94" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -9771,27 +9771,27 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9801,54 +9801,54 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q95" t="n">
         <v>0.31</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S95" t="n">
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U95" t="n">
         <v>3</v>
       </c>
       <c r="V95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W95" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
@@ -9870,22 +9870,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9905,33 +9905,33 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S96" t="n">
@@ -9941,13 +9941,13 @@
         <v>3</v>
       </c>
       <c r="U96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V96" t="n">
         <v>6</v>
       </c>
       <c r="W96" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
@@ -9969,47 +9969,47 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -10019,34 +10019,34 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S97" t="n">
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V97" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W97" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
@@ -10068,84 +10068,84 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t>fish</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P98" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q98" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S98" t="n">
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U98" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V98" t="n">
+        <v>11</v>
+      </c>
+      <c r="W98" t="n">
         <v>12</v>
-      </c>
-      <c r="W98" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -10167,44 +10167,44 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>center</t>
@@ -10221,10 +10221,10 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -10235,16 +10235,16 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U99" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V99" t="n">
+        <v>14</v>
+      </c>
+      <c r="W99" t="n">
         <v>5</v>
-      </c>
-      <c r="W99" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="100">
@@ -10266,52 +10266,52 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -10320,30 +10320,30 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S100" t="n">
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
@@ -10365,27 +10365,27 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10410,19 +10410,19 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -10433,16 +10433,16 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U101" t="n">
         <v>1</v>
       </c>
       <c r="V101" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="W101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -10464,22 +10464,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10489,17 +10489,17 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10509,19 +10509,19 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -10535,13 +10535,13 @@
         <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V102" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W102" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -10563,42 +10563,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_25.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -10631,16 +10631,16 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V103" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -10662,27 +10662,27 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_15.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -10712,34 +10712,34 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S104" t="n">
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U104" t="n">
         <v>11</v>
       </c>
       <c r="V104" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W104" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -10761,22 +10761,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>stimuli/car/car_31.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/house/house_08.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_23.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10801,28 +10801,28 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q105" t="n">
         <v>0.26</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S105" t="n">
@@ -10832,10 +10832,10 @@
         <v>11</v>
       </c>
       <c r="U105" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="V105" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W105" t="n">
         <v>12</v>

--- a/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_00.xlsx
+++ b/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_00.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -564,42 +564,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>guitar</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -632,16 +632,16 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
+        <v>12</v>
+      </c>
+      <c r="U2" t="n">
+        <v>14</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W2" t="n">
         <v>11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>12</v>
-      </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -652,7 +652,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -663,42 +663,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -731,16 +731,16 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -762,42 +762,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -830,16 +830,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
         <v>9</v>
       </c>
-      <c r="V4" t="n">
-        <v>6</v>
-      </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -850,7 +850,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -861,42 +861,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -929,16 +929,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -949,7 +949,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -960,42 +960,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1158,42 +1158,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1257,42 +1257,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1325,16 +1325,16 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>8</v>
+      </c>
+      <c r="W9" t="n">
         <v>10</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1356,42 +1356,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7</v>
-      </c>
       <c r="W10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1455,42 +1455,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1523,16 +1523,16 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1554,42 +1554,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1653,42 +1653,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,16 +1721,16 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1752,42 +1752,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1820,16 +1820,16 @@
         <v>14</v>
       </c>
       <c r="T14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>fish</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1919,16 +1919,16 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>11</v>
+      </c>
+      <c r="U15" t="n">
         <v>12</v>
       </c>
-      <c r="U15" t="n">
-        <v>14</v>
-      </c>
       <c r="V15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1950,42 +1950,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2018,16 +2018,16 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2049,42 +2049,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2117,16 +2117,16 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2148,42 +2148,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2216,16 +2216,16 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
-        <v>5</v>
-      </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2247,42 +2247,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2315,16 +2315,16 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2346,42 +2346,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2414,16 +2414,16 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" t="n">
         <v>10</v>
       </c>
-      <c r="U20" t="n">
-        <v>9</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7</v>
-      </c>
       <c r="W20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2445,42 +2445,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2544,42 +2544,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2612,16 +2612,16 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2643,42 +2643,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2742,42 +2742,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2810,16 +2810,16 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2841,42 +2841,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2909,16 +2909,16 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2940,42 +2940,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3039,42 +3039,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3107,16 +3107,16 @@
         <v>14</v>
       </c>
       <c r="T27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3138,42 +3138,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3206,16 +3206,16 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3237,42 +3237,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3305,16 +3305,16 @@
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3336,42 +3336,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3404,16 +3404,16 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3435,42 +3435,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3503,16 +3503,16 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5</v>
+      </c>
+      <c r="V31" t="n">
         <v>9</v>
       </c>
-      <c r="U31" t="n">
-        <v>3</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6</v>
-      </c>
       <c r="W31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3534,42 +3534,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3633,42 +3633,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3701,16 +3701,16 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3732,42 +3732,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3800,16 +3800,16 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3831,42 +3831,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3899,16 +3899,16 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
+        <v>7</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3</v>
+      </c>
+      <c r="W35" t="n">
         <v>10</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3930,42 +3930,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3998,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4029,42 +4029,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
+        <v>4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>14</v>
+      </c>
+      <c r="W37" t="n">
         <v>7</v>
-      </c>
-      <c r="V37" t="n">
-        <v>12</v>
-      </c>
-      <c r="W37" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4128,42 +4128,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4196,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
+        <v>2</v>
+      </c>
+      <c r="V38" t="n">
+        <v>12</v>
+      </c>
+      <c r="W38" t="n">
         <v>8</v>
-      </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4227,42 +4227,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4295,16 +4295,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4326,42 +4326,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4394,16 +4394,16 @@
         <v>14</v>
       </c>
       <c r="T40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4425,42 +4425,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>fish</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4493,16 +4493,16 @@
         <v>2</v>
       </c>
       <c r="T41" t="n">
+        <v>11</v>
+      </c>
+      <c r="U41" t="n">
         <v>12</v>
       </c>
-      <c r="U41" t="n">
-        <v>14</v>
-      </c>
       <c r="V41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4524,42 +4524,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4592,16 +4592,16 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U42" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4623,42 +4623,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4691,16 +4691,16 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4722,42 +4722,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4790,16 +4790,16 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
+        <v>9</v>
+      </c>
+      <c r="U44" t="n">
         <v>3</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>5</v>
       </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
       <c r="W44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4821,42 +4821,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4889,16 +4889,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4920,42 +4920,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4988,16 +4988,16 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5019,42 +5019,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5087,16 +5087,16 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V47" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W47" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -5118,42 +5118,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5186,16 +5186,16 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -5217,42 +5217,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U49" t="n">
+        <v>5</v>
+      </c>
+      <c r="V49" t="n">
         <v>1</v>
       </c>
-      <c r="V49" t="n">
-        <v>8</v>
-      </c>
       <c r="W49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -5316,42 +5316,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5415,42 +5415,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5483,16 +5483,16 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V51" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W51" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5514,42 +5514,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>car</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5582,16 +5582,16 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U52" t="n">
+        <v>13</v>
+      </c>
+      <c r="V52" t="n">
         <v>11</v>
       </c>
-      <c r="V52" t="n">
-        <v>12</v>
-      </c>
       <c r="W52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>fish</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5681,16 +5681,16 @@
         <v>14</v>
       </c>
       <c r="T53" t="n">
+        <v>13</v>
+      </c>
+      <c r="U53" t="n">
+        <v>15</v>
+      </c>
+      <c r="V53" t="n">
+        <v>2</v>
+      </c>
+      <c r="W53" t="n">
         <v>11</v>
-      </c>
-      <c r="U53" t="n">
-        <v>16</v>
-      </c>
-      <c r="V53" t="n">
-        <v>10</v>
-      </c>
-      <c r="W53" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -5712,42 +5712,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5780,16 +5780,16 @@
         <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U54" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -5811,42 +5811,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5879,16 +5879,16 @@
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W55" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5910,42 +5910,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -6009,42 +6009,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6077,16 +6077,16 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -6108,42 +6108,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6176,16 +6176,16 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -6207,42 +6207,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6275,16 +6275,16 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W59" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -6306,42 +6306,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6374,16 +6374,16 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U60" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V60" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -6405,42 +6405,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6473,16 +6473,16 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W61" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V62" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W62" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -6603,42 +6603,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6702,42 +6702,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,16 +6770,16 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
+      </c>
+      <c r="V64" t="n">
+        <v>3</v>
+      </c>
+      <c r="W64" t="n">
         <v>7</v>
-      </c>
-      <c r="U64" t="n">
-        <v>8</v>
-      </c>
-      <c r="V64" t="n">
-        <v>9</v>
-      </c>
-      <c r="W64" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -6801,42 +6801,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6869,16 +6869,16 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V65" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -6900,42 +6900,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6968,16 +6968,16 @@
         <v>14</v>
       </c>
       <c r="T66" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V66" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -6999,42 +6999,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>fish</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7067,16 +7067,16 @@
         <v>2</v>
       </c>
       <c r="T67" t="n">
+        <v>11</v>
+      </c>
+      <c r="U67" t="n">
         <v>12</v>
       </c>
-      <c r="U67" t="n">
-        <v>14</v>
-      </c>
       <c r="V67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W67" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -7098,42 +7098,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7166,16 +7166,16 @@
         <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W68" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -7197,42 +7197,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7265,16 +7265,16 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U69" t="n">
+        <v>9</v>
+      </c>
+      <c r="V69" t="n">
         <v>3</v>
       </c>
-      <c r="V69" t="n">
-        <v>5</v>
-      </c>
       <c r="W69" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -7296,42 +7296,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7364,16 +7364,16 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
+        <v>9</v>
+      </c>
+      <c r="U70" t="n">
         <v>3</v>
       </c>
-      <c r="U70" t="n">
-        <v>5</v>
-      </c>
       <c r="V70" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -7395,42 +7395,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7463,16 +7463,16 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U71" t="n">
+        <v>2</v>
+      </c>
+      <c r="V71" t="n">
         <v>10</v>
       </c>
-      <c r="V71" t="n">
-        <v>7</v>
-      </c>
       <c r="W71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -7494,42 +7494,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7562,16 +7562,16 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W72" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -7593,42 +7593,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7661,16 +7661,16 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
+        <v>6</v>
+      </c>
+      <c r="U73" t="n">
+        <v>10</v>
+      </c>
+      <c r="V73" t="n">
+        <v>12</v>
+      </c>
+      <c r="W73" t="n">
         <v>9</v>
-      </c>
-      <c r="U73" t="n">
-        <v>7</v>
-      </c>
-      <c r="V73" t="n">
-        <v>14</v>
-      </c>
-      <c r="W73" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -7692,42 +7692,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7760,16 +7760,16 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W74" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -7791,42 +7791,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U75" t="n">
+        <v>5</v>
+      </c>
+      <c r="V75" t="n">
         <v>1</v>
       </c>
-      <c r="V75" t="n">
-        <v>8</v>
-      </c>
       <c r="W75" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -7890,42 +7890,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7958,16 +7958,16 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U76" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V76" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W76" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -7989,42 +7989,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8057,16 +8057,16 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U77" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V77" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W77" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -8088,42 +8088,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8156,16 +8156,16 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U78" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V78" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W78" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -8187,42 +8187,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>fish</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8255,16 +8255,16 @@
         <v>14</v>
       </c>
       <c r="T79" t="n">
+        <v>13</v>
+      </c>
+      <c r="U79" t="n">
+        <v>15</v>
+      </c>
+      <c r="V79" t="n">
+        <v>6</v>
+      </c>
+      <c r="W79" t="n">
         <v>11</v>
-      </c>
-      <c r="U79" t="n">
-        <v>16</v>
-      </c>
-      <c r="V79" t="n">
-        <v>9</v>
-      </c>
-      <c r="W79" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="80">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -8286,42 +8286,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8354,16 +8354,16 @@
         <v>2</v>
       </c>
       <c r="T80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -8385,42 +8385,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8453,16 +8453,16 @@
         <v>3</v>
       </c>
       <c r="T81" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W81" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -8484,42 +8484,42 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8552,16 +8552,16 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U82" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -8583,42 +8583,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8651,16 +8651,16 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W83" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -8682,42 +8682,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8750,16 +8750,16 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U84" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W84" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -8781,42 +8781,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8849,16 +8849,16 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U85" t="n">
+        <v>9</v>
+      </c>
+      <c r="V85" t="n">
         <v>6</v>
       </c>
-      <c r="V85" t="n">
-        <v>4</v>
-      </c>
       <c r="W85" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -8880,42 +8880,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8948,16 +8948,16 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V86" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W86" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -8979,42 +8979,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9047,16 +9047,16 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
+        <v>7</v>
+      </c>
+      <c r="U87" t="n">
+        <v>6</v>
+      </c>
+      <c r="V87" t="n">
+        <v>1</v>
+      </c>
+      <c r="W87" t="n">
         <v>10</v>
-      </c>
-      <c r="U87" t="n">
-        <v>4</v>
-      </c>
-      <c r="V87" t="n">
-        <v>5</v>
-      </c>
-      <c r="W87" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -9078,42 +9078,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U88" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V88" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W88" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -9177,42 +9177,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U89" t="n">
+        <v>4</v>
+      </c>
+      <c r="V89" t="n">
+        <v>8</v>
+      </c>
+      <c r="W89" t="n">
         <v>7</v>
-      </c>
-      <c r="V89" t="n">
-        <v>1</v>
-      </c>
-      <c r="W89" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -9276,42 +9276,42 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9344,16 +9344,16 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="V90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W90" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -9375,42 +9375,42 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_19.jpg</t>
+          <t>stimuli/lamp/lamp_38.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9443,16 +9443,16 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W91" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -9474,42 +9474,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_22.jpg</t>
+          <t>stimuli/car/car_01.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/key/key_28.jpg</t>
+          <t>stimuli/pencil/pencil_31.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/car/car_36.jpg</t>
+          <t>stimuli/fish/fish_32.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9542,16 +9542,16 @@
         <v>14</v>
       </c>
       <c r="T92" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -9573,42 +9573,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
           <t>fish</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9641,16 +9641,16 @@
         <v>2</v>
       </c>
       <c r="T93" t="n">
+        <v>11</v>
+      </c>
+      <c r="U93" t="n">
         <v>12</v>
       </c>
-      <c r="U93" t="n">
-        <v>14</v>
-      </c>
       <c r="V93" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W93" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -9672,42 +9672,42 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9740,16 +9740,16 @@
         <v>3</v>
       </c>
       <c r="T94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="n">
+        <v>4</v>
+      </c>
+      <c r="W94" t="n">
         <v>8</v>
-      </c>
-      <c r="V94" t="n">
-        <v>6</v>
-      </c>
-      <c r="W94" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -9771,42 +9771,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9839,16 +9839,16 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W95" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -9870,42 +9870,42 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9938,16 +9938,16 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
+        <v>9</v>
+      </c>
+      <c r="U96" t="n">
         <v>3</v>
       </c>
-      <c r="U96" t="n">
-        <v>5</v>
-      </c>
       <c r="V96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W96" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -9969,42 +9969,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10037,16 +10037,16 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U97" t="n">
+        <v>2</v>
+      </c>
+      <c r="V97" t="n">
         <v>10</v>
       </c>
-      <c r="V97" t="n">
+      <c r="W97" t="n">
         <v>7</v>
-      </c>
-      <c r="W97" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="98">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -10068,42 +10068,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>fish</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10136,16 +10136,16 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U98" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V98" t="n">
+        <v>13</v>
+      </c>
+      <c r="W98" t="n">
         <v>11</v>
-      </c>
-      <c r="W98" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="99">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -10167,42 +10167,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10235,16 +10235,16 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V99" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -10266,42 +10266,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10334,16 +10334,16 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V100" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W100" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -10365,42 +10365,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10433,16 +10433,16 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V101" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W101" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -10464,42 +10464,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10532,16 +10532,16 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U102" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V102" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -10563,42 +10563,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10631,16 +10631,16 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U103" t="n">
+        <v>8</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1</v>
+      </c>
+      <c r="W103" t="n">
         <v>2</v>
-      </c>
-      <c r="V103" t="n">
-        <v>8</v>
-      </c>
-      <c r="W103" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -10662,42 +10662,42 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>car</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10730,16 +10730,16 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U104" t="n">
+        <v>13</v>
+      </c>
+      <c r="V104" t="n">
         <v>11</v>
       </c>
-      <c r="V104" t="n">
-        <v>12</v>
-      </c>
       <c r="W104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -10761,42 +10761,42 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>stimuli/car/car_01.jpg</t>
+          <t>stimuli/guitar/guitar_22.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_31.jpg</t>
+          <t>stimuli/key/key_28.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_38.jpg</t>
+          <t>stimuli/fish/fish_19.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_32.jpg</t>
+          <t>stimuli/car/car_36.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
           <t>car</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>fish</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10829,16 +10829,16 @@
         <v>14</v>
       </c>
       <c r="T105" t="n">
+        <v>13</v>
+      </c>
+      <c r="U105" t="n">
+        <v>15</v>
+      </c>
+      <c r="V105" t="n">
+        <v>12</v>
+      </c>
+      <c r="W105" t="n">
         <v>11</v>
-      </c>
-      <c r="U105" t="n">
-        <v>16</v>
-      </c>
-      <c r="V105" t="n">
-        <v>14</v>
-      </c>
-      <c r="W105" t="n">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
